--- a/excel/SingleAnalyteMU.xlsx
+++ b/excel/SingleAnalyteMU.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_56CD36E90A4EEFEBC2EB98F089B0D10D71361D3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FA49EF4-1D68-478E-9030-7A8E9F11B760}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="38" windowWidth="15960" windowHeight="18083" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="38" windowWidth="15960" windowHeight="18083" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MainTable" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,23 @@
     <sheet name="Units" sheetId="5" r:id="rId5"/>
     <sheet name="Notes" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -41,6 +58,9 @@
     <t>Select Report Type (Spike, Ref…) :</t>
   </si>
   <si>
+    <t>Low Spike</t>
+  </si>
+  <si>
     <t>Select Units (ppm, µg/kg, g/L…)    :</t>
   </si>
   <si>
@@ -212,6 +232,9 @@
     <t>S9 (Outlier?)</t>
   </si>
   <si>
+    <t>?58.97</t>
+  </si>
+  <si>
     <t>Report Date</t>
   </si>
   <si>
@@ -254,7 +277,13 @@
     <t>Bias as a %age</t>
   </si>
   <si>
+    <t>Is Bias Satisfactory? (Y/N)                          :</t>
+  </si>
+  <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Is Horwitz Ratio Satisfactory? (Y/N)            :</t>
   </si>
   <si>
     <t>Method Detection Limit (MDL)</t>
@@ -1470,25 +1499,13 @@
     <t>This spread-sheet is "Public Domain". Anyone is free to copy, modify, publish, use, or distribute it for any purpose, commercial or non-commercial, and by any means. The author is retired; carries out "Pro Bono" work only; and does not accept any responsibility for any loss caused by the use of, or failure to use, this spreadsheet.   Please do not remove my name, copyright &amp; version information.</t>
   </si>
   <si>
-    <t xml:space="preserve">Version: 2023-06-010   -   ©Tim Strutt. </t>
-  </si>
-  <si>
-    <t>Low Spike</t>
-  </si>
-  <si>
-    <t>Is Horwitz Ratio Satisfactory? (Y/N)            :</t>
-  </si>
-  <si>
-    <t>Is Bias Satisfactory? (Y/N)                          :</t>
-  </si>
-  <si>
-    <t>?58.97</t>
+    <t xml:space="preserve">Version: 2026-06-02   -   ©Tim Strutt. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
@@ -1497,7 +1514,7 @@
     <numFmt numFmtId="168" formatCode="d&quot; &quot;mmmm&quot; &quot;yyyy"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1796,12 +1813,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1841,7 +1852,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="86">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -1859,19 +1870,6 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
       <bottom style="thin">
         <color indexed="10"/>
       </bottom>
@@ -1897,18 +1895,9 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -1922,37 +1911,11 @@
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
         <color indexed="14"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2960,587 +2923,562 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="27" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="27" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="27" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="20" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="20" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="5" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="21" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="28" fillId="2" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="2" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="28" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="2" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="21" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="2" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="2" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="2" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="21" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="21" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="21" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3917,7 +3855,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle"/>
+        <xdr:cNvPr id="2" name="Rectangle">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3960,7 +3904,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle"/>
+        <xdr:cNvPr id="3" name="Rectangle">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4003,7 +3953,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle"/>
+        <xdr:cNvPr id="4" name="Rectangle">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4051,7 +4007,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rectangle"/>
+        <xdr:cNvPr id="6" name="Rectangle">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4094,7 +4056,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Rectangle"/>
+        <xdr:cNvPr id="11" name="Rectangle">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4142,7 +4110,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Shape 3"/>
+        <xdr:cNvPr id="13" name="Shape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4651,7 +4625,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Shape 4"/>
+        <xdr:cNvPr id="15" name="Shape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5822,575 +5802,580 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.1" customHeight="1" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.2" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="50.3125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="50.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.5" style="1" customWidth="1"/>
-    <col min="3" max="4" width="8.8125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="8.875" style="1" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="0.5" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.875" style="1" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="133" t="s">
+      <c r="B1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="172"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="172"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="135" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
+      <c r="B3" s="110" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="175"/>
+      <c r="D3" s="176"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="136" t="s">
+      <c r="A4" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="175"/>
+      <c r="D4" s="176"/>
     </row>
     <row r="5" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="137">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="112">
         <v>90</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="176"/>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="138"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="113"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="176"/>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="139">
+      <c r="A7" s="171" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="114">
         <v>2</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="str">
+      <c r="A8" s="173" t="str">
         <f>IF(B8=2,IF(B24&lt;9,"Number of Samples = "&amp;B24&amp;" Try Selecting 1-tail test","Select One or Two tail Grubbs’ Test (α: 0.05) :"),"Select One or Two tail Grubbs’ Test (α: 0.05) :")</f>
-        <v>Number of Samples = 8 Try Selecting 1-tail test</v>
-      </c>
-      <c r="B8" s="140">
-        <v>2</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
+        <v>Select One or Two tail Grubbs’ Test (α: 0.05) :</v>
+      </c>
+      <c r="B8" s="115">
+        <v>1</v>
+      </c>
+      <c r="C8" s="175"/>
+      <c r="D8" s="176"/>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="13" t="str">
+      <c r="A9" s="178" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="179" t="str">
         <f>IF(B38&gt;0,B24+B38&amp;" ("&amp;B38&amp;"  Excluded)",B24)</f>
         <v>9 (1  Excluded)</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="176"/>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A10" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="15" t="str">
+      <c r="A10" s="180" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="181" t="str">
         <f>FIXED(B26,B27)</f>
         <v>6.377</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="175"/>
+      <c r="D10" s="176"/>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="182">
         <f>B28</f>
         <v>7.667658640694984E-2</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="176"/>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="16">
+      <c r="A12" s="180" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="182">
         <f>IFERROR(IF(B3="Blank",0,(1-B22)),0)</f>
         <v>7.5916666666666743E-2</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
+      <c r="C12" s="175"/>
+      <c r="D12" s="176"/>
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="18">
+      <c r="A13" s="183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="184">
         <f>VLOOKUP(B24-1,Distributions!A2:B42,2,TRUE)</f>
         <v>2.9980000000000002</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="176"/>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="19">
+      <c r="A14" s="178" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="185">
         <f>VLOOKUP(B4,Units!$A1:$B14,2,FALSE)</f>
         <v>1000000000</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="175"/>
+      <c r="D14" s="176"/>
     </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="180" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="186">
         <f>IF(B5/B14&lt;1.2*0.0000001,22,IF(B5/B14&lt;=0.138,2*POWER(B5/B14,-0.15),POWER(B5/B14,-0.5)))</f>
         <v>22</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
+      <c r="C15" s="175"/>
+      <c r="D15" s="176"/>
     </row>
     <row r="16" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A16" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="21">
+      <c r="A16" s="183" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="5">
         <f>((B11*100)/B15)</f>
         <v>0.34852993821340833</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="175"/>
+      <c r="D16" s="176"/>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A17" s="22" t="str">
+      <c r="A17" s="187" t="str">
         <f>IF(B17=B36,"Ymax (Maximum Value) may be a Grubbs' Outlier","Ymax (Maximum Value)")</f>
         <v>Ymax (Maximum Value)</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="179">
         <f>MAX(SampleResults!B1:B31)</f>
         <v>89.84</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
+      <c r="C17" s="175"/>
+      <c r="D17" s="176"/>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A18" s="23" t="str">
+      <c r="A18" s="188" t="str">
         <f>IF(B18=B36,"Ymin (Minimum Value) may be a Grubbs' Outlier","Ymin  (Minimum Value)")</f>
         <v>Ymin  (Minimum Value)</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="184">
         <f>MIN(SampleResults!B1:B31)</f>
         <v>72.11</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="176"/>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A19" s="24" t="str">
+      <c r="A19" s="189" t="str">
         <f>"Result to "&amp;B7&amp;" Significant figures"</f>
         <v>Result to 2 Significant figures</v>
       </c>
-      <c r="B19" s="25" t="str">
+      <c r="B19" s="190" t="str">
         <f>FIXED(B25,((-1*INT(LOG10(B25)))-1)+B7,TRUE)</f>
         <v>83</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="176"/>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="27" t="str">
+      <c r="A20" s="191" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="192" t="str">
         <f>IFERROR(IF(B3="Blank",0,B51),0)</f>
         <v>21</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="176"/>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="29" t="str">
+      <c r="A21" s="191" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="192" t="str">
         <f>IFERROR(IF(B3="Blank",0,B45),0)</f>
         <v>62</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="176"/>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7">
         <f>IFERROR(IF(B3="Blank","Blank",(B25)/B5),100)</f>
         <v>0.92408333333333326</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="176"/>
     </row>
     <row r="23" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A23" s="33"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="176"/>
     </row>
     <row r="24" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A24" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="37">
+      <c r="A24" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="13">
         <f>COUNT(SampleResults!B1:B31)</f>
         <v>8</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="8"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="176"/>
     </row>
     <row r="25" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A25" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="39">
+      <c r="A25" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="15">
         <f>IF(B24&gt;0,AVERAGE(SampleResults!B1:B31),0)</f>
         <v>83.16749999999999</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="8"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="176"/>
     </row>
     <row r="26" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A26" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="40">
+      <c r="A26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="16">
         <f>IF(B24&gt;1,STDEV(SampleResults!B1:B31),0)</f>
         <v>6.3774754297561085</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="176"/>
     </row>
     <row r="27" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A27" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="42">
+      <c r="A27" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="18">
         <f>IF(B5&lt;1,INT(ABS(LOG10(B5)))+B7+2,IF(B5&lt;10,4,IF(B5&lt;100,3,IF(B5&lt;1000,2,IF(B5&lt;10000,1,0)))))</f>
         <v>3</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="8"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="176"/>
     </row>
     <row r="28" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A28" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="42">
+      <c r="A28" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="18">
         <f>IF(B24&gt;0,B10/B25,0)</f>
         <v>7.667658640694984E-2</v>
       </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="8"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="176"/>
     </row>
     <row r="29" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="8"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="176"/>
     </row>
     <row r="30" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A30" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="44">
+      <c r="A30" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="20">
         <f>B17-B25</f>
         <v>6.6725000000000136</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="176"/>
     </row>
     <row r="31" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A31" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="45">
+      <c r="A31" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="21">
         <f>B25-B18</f>
         <v>11.05749999999999</v>
       </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="8"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="176"/>
     </row>
     <row r="32" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A32" s="38" t="str">
+      <c r="A32" s="14" t="str">
         <f>IF(B8=1,"Sig Value: 1-sided","Sig Value: 2-sided")</f>
-        <v>Sig Value: 2-sided</v>
-      </c>
-      <c r="B32" s="46">
+        <v>Sig Value: 1-sided</v>
+      </c>
+      <c r="B32" s="22">
         <f>IF(B8=1,(2*(1-0.95))/(B24),((1-0.95))/(B24))</f>
-        <v>6.2500000000000056E-3</v>
-      </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="8"/>
+        <v>1.2500000000000011E-2</v>
+      </c>
+      <c r="C32" s="11"/>
+      <c r="D32" s="176"/>
     </row>
     <row r="33" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A33" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="46">
+      <c r="A33" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="22">
         <f>(B25-B18)/B26</f>
         <v>1.7338365504957904</v>
       </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="8"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="176"/>
     </row>
     <row r="34" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A34" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="46">
+      <c r="A34" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="22">
         <f>(B17-B25)/B26</f>
         <v>1.0462604009209311</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="176"/>
     </row>
     <row r="35" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A35" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="47">
+      <c r="A35" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="23">
         <f>VLOOKUP(B24,Distributions!A5:D42,(2+B8))</f>
-        <v>2.1259999999999999</v>
-      </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="8"/>
+        <v>2.032</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="176"/>
     </row>
     <row r="36" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A36" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="42">
+      <c r="A36" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="18">
         <f>IFERROR(IF(B33&lt;B35,IF(B34&lt;B35,0,B17),B18),0)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="8"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="176"/>
     </row>
     <row r="37" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A37" s="48"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="8"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="176"/>
     </row>
     <row r="38" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A38" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="47">
+      <c r="A38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="23">
         <f>COUNTIF(SampleResults!B1:B31,"*")</f>
         <v>1</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="176"/>
     </row>
     <row r="39" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A39" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="46">
+      <c r="A39" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="22">
         <f>SQRT(POWER(B26,2)+POWER(B26/SQRT(B24),2))</f>
         <v>6.764334184846704</v>
       </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="8"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="176"/>
     </row>
     <row r="40" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A40" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="46">
+      <c r="A40" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="22">
         <f>IF(ISBLANK(B6),B13*B26,B6)</f>
         <v>19.119671338408814</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="8"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="176"/>
     </row>
     <row r="41" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A41" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="46">
+      <c r="A41" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="22">
         <f>B39*2</f>
         <v>13.528668369693408</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="8"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="176"/>
     </row>
     <row r="42" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A42" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="50">
+      <c r="A42" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="26">
         <f>B25-B5</f>
         <v>-6.8325000000000102</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="8"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="176"/>
     </row>
     <row r="43" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A43" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="52">
+      <c r="A43" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="28">
         <f>IF(ISTEXT(B6),B19,IFERROR(B40/B22,IF(B6&gt;0,B6,B19)))</f>
         <v>20.690418979250229</v>
       </c>
-      <c r="C43" s="53"/>
-      <c r="D43" s="54"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="30"/>
     </row>
     <row r="44" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A44" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="56">
+      <c r="A44" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="32">
         <f>B43*3</f>
         <v>62.07125693775069</v>
       </c>
-      <c r="C44" s="53"/>
-      <c r="D44" s="54"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="30"/>
     </row>
     <row r="45" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A45" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="57" t="str">
+      <c r="A45" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="33" t="str">
         <f>FIXED(B44,((-1*INT(LOG10(B44)))-1)+B7,TRUE)</f>
         <v>62</v>
       </c>
-      <c r="C45" s="53"/>
-      <c r="D45" s="54"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A46" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="59" t="str">
+      <c r="A46" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="35" t="str">
         <f>FIXED(B5,((-1*INT(LOG10(B5)))-1)+B7,TRUE)</f>
         <v>90</v>
       </c>
-      <c r="C46" s="53"/>
-      <c r="D46" s="54"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="30"/>
     </row>
     <row r="47" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A47" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="60"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="8"/>
+      <c r="A47" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="36"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="176"/>
     </row>
     <row r="48" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A48" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="61">
+      <c r="A48" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="37">
         <f>INT(LOG10(B46))</f>
         <v>1</v>
       </c>
-      <c r="C48" s="53"/>
-      <c r="D48" s="54"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="30"/>
     </row>
     <row r="49" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A49" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="61">
+      <c r="A49" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="37">
         <f>INT(LOG10(B43))</f>
         <v>1</v>
       </c>
-      <c r="C49" s="53"/>
-      <c r="D49" s="54"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="30"/>
     </row>
     <row r="50" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A50" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="56">
+      <c r="A50" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="32">
         <f>IF(B48=B49,1,B48-B49+1)</f>
         <v>1</v>
       </c>
-      <c r="C50" s="53"/>
-      <c r="D50" s="54"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="30"/>
     </row>
     <row r="51" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A51" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="59" t="str">
+      <c r="A51" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="35" t="str">
         <f>FIXED(B43,((-1*INT(LOG10(B43)))-B50)+B7,TRUE)</f>
         <v>21</v>
       </c>
-      <c r="C51" s="53"/>
-      <c r="D51" s="54"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="30"/>
     </row>
     <row r="52" spans="1:4" ht="9" hidden="1" customHeight="1">
-      <c r="A52" s="62"/>
-      <c r="B52" s="63"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
+      <c r="A52" s="38"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="193"/>
     </row>
     <row r="53" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A53" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="67" t="str">
+      <c r="A53" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="42" t="str">
         <f>IF(ISTEXT(B6),"MDL not a Number!",IFERROR(IF(B3="Blank","Blank: "&amp;B51&amp;" "&amp;IF(B6&gt;0,"^"&amp;B4,B4),IF(B6&gt;B5,"MDL &gt; Spike!",IF(B6&gt;0,B46&amp;" ± "&amp;B51&amp;" ^"&amp;B4,B46&amp;" ± "&amp;B51&amp;" "&amp;B4))),"Error!!"))</f>
         <v>90 ± 21 µg/kg</v>
       </c>
-      <c r="C53" s="64"/>
-      <c r="D53" s="65"/>
-    </row>
-    <row r="54" spans="1:4" ht="15.1" customHeight="1"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="193"/>
+    </row>
+    <row r="54" spans="1:4" ht="15.2" customHeight="1">
+      <c r="A54" s="100"/>
+      <c r="B54" s="100"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="100"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pEIbC+Wmoaa0j6T3cAF8oYoune0UxC6Kn28oj4PjPVS5XhJWr0HlGG5kO86ckNqNhFmVg2+p1MYSA6orjqz6Cw==" saltValue="YuOV1/hU1ztUF4mh/lzmSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="A5">
     <cfRule type="containsBlanks" dxfId="30" priority="5" stopIfTrue="1">
       <formula>ISBLANK(A5)</formula>
@@ -6503,16 +6488,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Spike,Blank,Low Spike,Reference Material"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4">
-      <formula1>"ppm,ppb,ppt,mg/kg,µg/kg,ng/kg,mg/L,µg/L,ng/L,pg/L,g/L,drops/floz"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"ppm,ppb,ppt,mg/kg,µg/kg,ng/kg,mg/L,µg/L,ng/L,pg/L,g/L,percent,drops/floz"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"2,1,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6526,331 +6511,331 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.875" style="157" customWidth="1"/>
-    <col min="2" max="2" width="17.6875" style="152" customWidth="1"/>
-    <col min="3" max="7" width="8.8125" style="152" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="0.125" style="152" customWidth="1"/>
-    <col min="9" max="16384" width="8.875" style="152" hidden="1"/>
+    <col min="1" max="1" width="31.875" style="125" customWidth="1"/>
+    <col min="2" max="2" width="17.75" style="121" customWidth="1"/>
+    <col min="3" max="7" width="8.875" style="121" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="0.125" style="121" customWidth="1"/>
+    <col min="9" max="16384" width="8.875" style="121" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A1" s="141" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="142">
+    <row r="1" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A1" s="194" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="195">
         <v>86.38</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-    </row>
-    <row r="2" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A2" s="143" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="144">
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+    </row>
+    <row r="2" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A2" s="118" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="119">
         <v>87.79</v>
       </c>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-    </row>
-    <row r="3" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A3" s="143" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="145">
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+    </row>
+    <row r="3" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A3" s="118" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="119">
         <v>77.94</v>
       </c>
-      <c r="C3" s="153"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
-      <c r="F3" s="153"/>
-      <c r="G3" s="153"/>
-    </row>
-    <row r="4" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A4" s="143" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="145">
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+    </row>
+    <row r="4" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A4" s="118" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="119">
         <v>72.11</v>
       </c>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="153"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A5" s="143" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="145">
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A5" s="118" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="119">
         <v>78.56</v>
       </c>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-    </row>
-    <row r="6" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A6" s="143" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="144">
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+    </row>
+    <row r="6" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A6" s="118" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="119">
         <v>89.84</v>
       </c>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-    </row>
-    <row r="7" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A7" s="143" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="144">
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+    </row>
+    <row r="7" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A7" s="118" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="119">
         <v>89.3</v>
       </c>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A8" s="143" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="144">
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+    </row>
+    <row r="8" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A8" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="119">
         <v>83.42</v>
       </c>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="153"/>
-      <c r="G8" s="153"/>
-    </row>
-    <row r="9" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A9" s="143" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="144" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
-      <c r="G9" s="153"/>
-    </row>
-    <row r="10" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A10" s="143"/>
-      <c r="B10" s="144"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="153"/>
-    </row>
-    <row r="11" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A11" s="148"/>
-      <c r="B11" s="150"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-    </row>
-    <row r="12" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A12" s="148"/>
-      <c r="B12" s="150"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="154"/>
-      <c r="E12" s="154"/>
-      <c r="F12" s="154"/>
-      <c r="G12" s="154"/>
-    </row>
-    <row r="13" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A13" s="148"/>
-      <c r="B13" s="150"/>
-      <c r="C13" s="154"/>
-      <c r="D13" s="154"/>
-      <c r="E13" s="154"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="154"/>
-    </row>
-    <row r="14" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A14" s="148"/>
-      <c r="B14" s="150"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154"/>
-      <c r="G14" s="154"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A15" s="148"/>
-      <c r="B15" s="150"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="154"/>
-    </row>
-    <row r="16" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A16" s="143"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="153"/>
-      <c r="G16" s="153"/>
-    </row>
-    <row r="17" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A17" s="143"/>
-      <c r="B17" s="145"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="153"/>
-    </row>
-    <row r="18" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A18" s="148"/>
-      <c r="B18" s="149"/>
-      <c r="C18" s="154"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="154"/>
-      <c r="G18" s="154"/>
-    </row>
-    <row r="19" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A19" s="148"/>
-      <c r="B19" s="149"/>
-      <c r="C19" s="154"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="154"/>
-      <c r="F19" s="154"/>
-      <c r="G19" s="154"/>
-    </row>
-    <row r="20" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A20" s="148"/>
-      <c r="B20" s="149"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
-    </row>
-    <row r="21" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A21" s="143"/>
-      <c r="B21" s="144"/>
-      <c r="C21" s="153"/>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="153"/>
-      <c r="G21" s="153"/>
-    </row>
-    <row r="22" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A22" s="143"/>
-      <c r="B22" s="144"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-    </row>
-    <row r="23" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A23" s="143"/>
-      <c r="B23" s="144"/>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="153"/>
-      <c r="G23" s="153"/>
-    </row>
-    <row r="24" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A24" s="143"/>
-      <c r="B24" s="144"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153"/>
-      <c r="G24" s="153"/>
-    </row>
-    <row r="25" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A25" s="143"/>
-      <c r="B25" s="144"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="153"/>
-    </row>
-    <row r="26" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A26" s="143"/>
-      <c r="B26" s="144"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
-      <c r="F26" s="153"/>
-      <c r="G26" s="153"/>
-    </row>
-    <row r="27" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A27" s="143"/>
-      <c r="B27" s="144"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-    </row>
-    <row r="28" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A28" s="143"/>
-      <c r="B28" s="144"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-    </row>
-    <row r="29" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A29" s="143"/>
-      <c r="B29" s="144"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="153"/>
-    </row>
-    <row r="30" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A30" s="143"/>
-      <c r="B30" s="144"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="155"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-    </row>
-    <row r="31" spans="1:7" ht="16.600000000000001" customHeight="1">
-      <c r="A31" s="146"/>
-      <c r="B31" s="147"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="155"/>
-      <c r="G31" s="155"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="122"/>
+    </row>
+    <row r="9" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A9" s="118" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+    </row>
+    <row r="10" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="122"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+    </row>
+    <row r="11" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A12" s="118"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A13" s="118"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+    </row>
+    <row r="14" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A14" s="118"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A15" s="118"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+    </row>
+    <row r="16" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A16" s="118"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+    </row>
+    <row r="17" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A17" s="118"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+    </row>
+    <row r="18" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A18" s="118"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+    </row>
+    <row r="19" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A19" s="118"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+    </row>
+    <row r="20" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A20" s="118"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+    </row>
+    <row r="21" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A21" s="118"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+    </row>
+    <row r="22" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A22" s="118"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="122"/>
+    </row>
+    <row r="23" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A23" s="118"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122"/>
+    </row>
+    <row r="24" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A24" s="118"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+    </row>
+    <row r="25" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A25" s="118"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="122"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="122"/>
+    </row>
+    <row r="26" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A26" s="118"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="122"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A27" s="118"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+    </row>
+    <row r="28" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A28" s="118"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+    </row>
+    <row r="29" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A29" s="118"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+    </row>
+    <row r="30" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A30" s="118"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="122"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="122"/>
+    </row>
+    <row r="31" spans="1:7" ht="16.7" customHeight="1">
+      <c r="A31" s="116"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="123"/>
+      <c r="G31" s="123"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="XznqIcz1YTVc5glUFaaIXnqZRrAb6dPBbIXrHXDmxz4JIGOBiUjXajKJ4qMHifPYC9fobntkRTReccZl6WsONQ==" saltValue="6YBrDahtS7mvBvGhb86fqA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -6872,407 +6857,411 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="46.8125" style="161" customWidth="1"/>
-    <col min="2" max="2" width="46.75" style="161" customWidth="1"/>
-    <col min="3" max="3" width="8.8125" style="161" hidden="1" customWidth="1"/>
-    <col min="4" max="6" width="8.8125" style="68" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="0.5" style="68" customWidth="1"/>
-    <col min="8" max="8" width="0" style="68" hidden="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.875" style="68" hidden="1"/>
+    <col min="1" max="1" width="46.875" style="129" customWidth="1"/>
+    <col min="2" max="2" width="46.75" style="129" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="129" hidden="1" customWidth="1"/>
+    <col min="4" max="6" width="8.875" style="43" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="0.5" style="43" customWidth="1"/>
+    <col min="8" max="8" width="0" style="43" hidden="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.875" style="43" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="125" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="161"/>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-    </row>
-    <row r="2" spans="1:6" s="160" customFormat="1" ht="16.350000000000001" customHeight="1">
-      <c r="A2" s="201" t="str">
+    <row r="1" spans="1:6" s="100" customFormat="1" ht="15" customHeight="1">
+      <c r="A1" s="129"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+    </row>
+    <row r="2" spans="1:6" s="128" customFormat="1" ht="16.350000000000001" customHeight="1">
+      <c r="A2" s="169" t="str">
         <f>"Summary Report - "&amp;B17</f>
         <v>Summary Report - Low Spike</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-    </row>
-    <row r="3" spans="1:6" s="160" customFormat="1" ht="14.35" customHeight="1">
-      <c r="A3" s="199"/>
-      <c r="B3" s="200"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A4" s="162" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="178">
+      <c r="B2" s="170"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+    </row>
+    <row r="3" spans="1:6" s="128" customFormat="1" ht="14.45" customHeight="1">
+      <c r="A3" s="167"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A4" s="130" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="146">
         <v>44676</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A5" s="162" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="179" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A6" s="162" t="s">
+      <c r="C4" s="99"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A5" s="130" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="179" t="s">
+      <c r="B5" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="124"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A7" s="162"/>
-      <c r="B7" s="179" t="s">
+      <c r="C5" s="99"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A6" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="124"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A8" s="162"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A9" s="162" t="s">
+      <c r="B6" s="147" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="179" t="s">
+      <c r="C6" s="99"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A7" s="130"/>
+      <c r="B7" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="124"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-    </row>
-    <row r="10" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A10" s="167"/>
-      <c r="B10" s="179" t="s">
+      <c r="C7" s="99"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A8" s="130"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A9" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="124"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A11" s="166"/>
-      <c r="B11" s="180"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A12" s="162" t="s">
+      <c r="B9" s="147" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="179" t="s">
+      <c r="C9" s="99"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A10" s="135"/>
+      <c r="B10" s="147" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="124"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A11" s="134"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A12" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="147" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="99"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
     </row>
     <row r="13" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A13" s="163"/>
-      <c r="B13" s="181"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
+      <c r="A13" s="131"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="14" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A14" s="164"/>
-      <c r="B14" s="182"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A15" s="165" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="183" t="str">
+      <c r="A14" s="132"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+    </row>
+    <row r="15" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A15" s="133" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="151" t="str">
         <f>MainTable!B2</f>
         <v>Acrylamide</v>
       </c>
-      <c r="C15" s="124"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A16" s="165" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="184">
+      <c r="C15" s="99"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A16" s="133" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="152">
         <f>MainTable!B24</f>
         <v>8</v>
       </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A17" s="166" t="str">
+      <c r="C16" s="99"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+    </row>
+    <row r="17" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A17" s="134" t="str">
         <f>IF(B17&lt;&gt;"Certified Reference","Report Type","Reporting Type NOT yet installed...")</f>
         <v>Report Type</v>
       </c>
-      <c r="B17" s="185" t="str">
+      <c r="B17" s="153" t="str">
         <f>MainTable!B3</f>
         <v>Low Spike</v>
       </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A18" s="167" t="str">
+      <c r="C17" s="99"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+    </row>
+    <row r="18" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A18" s="135" t="str">
         <f>IF(B17="Reference Material","Reference Material Type (PT, CRM, Lab., etc.)","")</f>
         <v/>
       </c>
-      <c r="B18" s="186"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A19" s="165" t="str">
+      <c r="B18" s="154"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A19" s="133" t="str">
         <f>IF(B17="Reference Material","ReferenceID: (PT, Batch/SerialNo., Date, etc.)","")</f>
         <v/>
       </c>
-      <c r="B19" s="187"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A20" s="168" t="str">
+      <c r="B19" s="155"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+    </row>
+    <row r="20" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A20" s="136" t="str">
         <f>IF(B17="Reference Material","Reference Material Uncertainty: "&amp;MainTable!B4&amp;" (info only)","")</f>
         <v/>
       </c>
-      <c r="B20" s="187"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-    </row>
-    <row r="21" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A21" s="166" t="str">
+      <c r="B20" s="155"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+    </row>
+    <row r="21" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A21" s="134" t="str">
         <f>B17&amp;" Level"</f>
         <v>Low Spike Level</v>
       </c>
-      <c r="B21" s="185" t="str">
+      <c r="B21" s="153" t="str">
         <f>MainTable!B5&amp;" "&amp;MainTable!B4</f>
         <v>90 µg/kg</v>
       </c>
-      <c r="C21" s="124"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="1:6" ht="16.149999999999999" customHeight="1">
-      <c r="A22" s="167" t="str">
+      <c r="A22" s="135" t="str">
         <f>MainTable!$A22</f>
         <v>% Recovery</v>
       </c>
-      <c r="B22" s="188">
+      <c r="B22" s="156">
         <f>IF(MainTable!B3="Blank","Blank",MainTable!B22)</f>
         <v>0.92408333333333326</v>
       </c>
-      <c r="C22" s="124"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
     </row>
     <row r="23" spans="1:6" ht="16.149999999999999" customHeight="1">
-      <c r="A23" s="166" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="189">
+      <c r="A23" s="134" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="157">
         <f>MainTable!B11</f>
         <v>7.667658640694984E-2</v>
       </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A24" s="162" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="190">
+      <c r="C23" s="99"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+    </row>
+    <row r="24" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A24" s="130" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="158">
         <f>MainTable!B12</f>
         <v>7.5916666666666743E-2</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A25" s="169" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="191" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="124"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-    </row>
-    <row r="26" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A26" s="167" t="str">
+      <c r="C24" s="99"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+    </row>
+    <row r="25" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A25" s="137" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="159" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="99"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+    </row>
+    <row r="26" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A26" s="135" t="str">
         <f>MainTable!$A16</f>
         <v xml:space="preserve">Horwitz Ratio (Ideally 0.3≤ HorRat ≤1)   </v>
       </c>
-      <c r="B26" s="192">
+      <c r="B26" s="160">
         <f>MainTable!B16</f>
         <v>0.34852993821340833</v>
       </c>
-      <c r="C26" s="124"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A27" s="170" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="193" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="124"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+    </row>
+    <row r="27" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A27" s="138" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="99"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
     </row>
     <row r="28" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A28" s="171"/>
-      <c r="B28" s="194"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
+      <c r="A28" s="139"/>
+      <c r="B28" s="162"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
     </row>
     <row r="29" spans="1:6" ht="16.350000000000001" customHeight="1">
-      <c r="A29" s="172"/>
-      <c r="B29" s="195"/>
-      <c r="C29" s="124"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A30" s="173" t="str">
+      <c r="A29" s="140"/>
+      <c r="B29" s="163"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A30" s="141" t="str">
         <f>"Result to "&amp;MainTable!B7&amp;" Significant figures"</f>
         <v>Result to 2 Significant figures</v>
       </c>
-      <c r="B30" s="196" t="str">
+      <c r="B30" s="164" t="str">
         <f>MainTable!B19&amp;" "&amp;MainTable!B4</f>
         <v>83 µg/kg</v>
       </c>
-      <c r="C30" s="124"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A31" s="174" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="197" t="str">
+      <c r="C30" s="99"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+    </row>
+    <row r="31" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A31" s="142" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="165" t="str">
         <f>IF(MainTable!B3="Blank",0,MainTable!B20&amp;" "&amp;MainTable!B4)</f>
         <v>21 µg/kg</v>
       </c>
-      <c r="C31" s="124"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A32" s="174" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="197" t="str">
+      <c r="C31" s="99"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+    </row>
+    <row r="32" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A32" s="142" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="165" t="str">
         <f>IF(MainTable!B3="Blank",0,MainTable!B21&amp;" "&amp;MainTable!B4)</f>
         <v>62 µg/kg</v>
       </c>
-      <c r="C32" s="124"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-    </row>
-    <row r="33" spans="1:6" ht="16.600000000000001" customHeight="1">
-      <c r="A33" s="175" t="str">
+      <c r="C32" s="99"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+    </row>
+    <row r="33" spans="1:6" ht="16.7" customHeight="1">
+      <c r="A33" s="143" t="str">
         <f>IF(B27&amp;B25="YesYes","Result Corrected for Recovery Bias","Horwitz Ratio / Bias Not Approved")</f>
         <v>Result Corrected for Recovery Bias</v>
       </c>
-      <c r="B33" s="198" t="str">
+      <c r="B33" s="166" t="str">
         <f>MainTable!B53</f>
         <v>90 ± 21 µg/kg</v>
       </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" hidden="1" customHeight="1">
-      <c r="A34" s="176"/>
-      <c r="B34" s="176"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-    </row>
-    <row r="35" spans="1:6" s="161" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="177"/>
-      <c r="B35" s="177"/>
-      <c r="C35" s="124"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1"/>
+      <c r="A34" s="144"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+    </row>
+    <row r="35" spans="1:6" s="129" customFormat="1" ht="15" customHeight="1">
+      <c r="A35" s="145"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1">
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+    </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Nc2c4xDjDd6kXdN/0botDMQN9flx8DW84tsyuo102YxGrnBWg6bPOne+osqfittLQUnwG8K6pbRvUS44L1xdTg==" saltValue="GnomyLSBZgphW0oufaPg5g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="A17">
@@ -7303,7 +7292,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25 B27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25 B27" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Choose Y/N,Yes,Not Satisfactory"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7317,830 +7306,830 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="74" customWidth="1"/>
-    <col min="2" max="2" width="16" style="74" customWidth="1"/>
-    <col min="3" max="3" width="14.1875" style="74" customWidth="1"/>
-    <col min="4" max="4" width="14.6875" style="74" customWidth="1"/>
-    <col min="5" max="10" width="8.8125" style="74" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="0.6875" style="74" customWidth="1"/>
-    <col min="12" max="16384" width="8.875" style="74" hidden="1"/>
+    <col min="1" max="1" width="15.375" style="49" customWidth="1"/>
+    <col min="2" max="2" width="16" style="49" customWidth="1"/>
+    <col min="3" max="3" width="14.25" style="49" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="49" customWidth="1"/>
+    <col min="5" max="10" width="8.875" style="49" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="0.75" style="49" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="49" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="203" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="205" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="4"/>
+      <c r="A1" s="196" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="197"/>
+      <c r="C1" s="198" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="199"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="172"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A2" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="77">
+      <c r="A2" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="52">
         <v>0.99</v>
       </c>
-      <c r="C2" s="78" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="79" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
+      <c r="C2" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A3" s="81">
+      <c r="A3" s="56">
         <v>1</v>
       </c>
-      <c r="B3" s="82">
+      <c r="B3" s="57">
         <v>31.82</v>
       </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A4" s="86">
+      <c r="A4" s="61">
         <v>2</v>
       </c>
-      <c r="B4" s="87">
+      <c r="B4" s="62">
         <v>6.9649999999999999</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A5" s="90">
+      <c r="A5" s="65">
         <v>3</v>
       </c>
-      <c r="B5" s="91">
+      <c r="B5" s="66">
         <v>4.5410000000000004</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="67">
         <v>1.153</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="68">
         <v>1.155</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A6" s="86">
+      <c r="A6" s="61">
         <v>4</v>
       </c>
-      <c r="B6" s="87">
+      <c r="B6" s="62">
         <v>3.7469999999999999</v>
       </c>
-      <c r="C6" s="94">
+      <c r="C6" s="69">
         <v>1.4630000000000001</v>
       </c>
-      <c r="D6" s="95">
+      <c r="D6" s="70">
         <v>1.4810000000000001</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A7" s="90">
+      <c r="A7" s="65">
         <v>5</v>
       </c>
-      <c r="B7" s="91">
+      <c r="B7" s="66">
         <v>3.3650000000000002</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="67">
         <v>1.6719999999999999</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="68">
         <v>1.7150000000000001</v>
       </c>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A8" s="86">
+      <c r="A8" s="61">
         <v>6</v>
       </c>
-      <c r="B8" s="87">
+      <c r="B8" s="62">
         <v>3.1429999999999998</v>
       </c>
-      <c r="C8" s="94">
+      <c r="C8" s="69">
         <v>1.8220000000000001</v>
       </c>
-      <c r="D8" s="95">
+      <c r="D8" s="70">
         <v>1.887</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="85"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A9" s="90">
+      <c r="A9" s="65">
         <v>7</v>
       </c>
-      <c r="B9" s="91">
+      <c r="B9" s="66">
         <v>2.9980000000000002</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="67">
         <v>1.9379999999999999</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="68">
         <v>2.02</v>
       </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="85"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A10" s="86">
+      <c r="A10" s="61">
         <v>8</v>
       </c>
-      <c r="B10" s="87">
+      <c r="B10" s="62">
         <v>2.8959999999999999</v>
       </c>
-      <c r="C10" s="94">
+      <c r="C10" s="69">
         <v>2.032</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="70">
         <v>2.1259999999999999</v>
       </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="85"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A11" s="90">
+      <c r="A11" s="65">
         <v>9</v>
       </c>
-      <c r="B11" s="91">
+      <c r="B11" s="66">
         <v>2.8210000000000002</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="67">
         <v>2.11</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="68">
         <v>2.2149999999999999</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A12" s="86">
+      <c r="A12" s="61">
         <v>10</v>
       </c>
-      <c r="B12" s="87">
+      <c r="B12" s="62">
         <v>2.7639999999999998</v>
       </c>
-      <c r="C12" s="94">
+      <c r="C12" s="69">
         <v>2.1760000000000002</v>
       </c>
-      <c r="D12" s="95">
+      <c r="D12" s="70">
         <v>2.29</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A13" s="90">
+      <c r="A13" s="65">
         <v>11</v>
       </c>
-      <c r="B13" s="91">
+      <c r="B13" s="66">
         <v>2.718</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="67">
         <v>2.234</v>
       </c>
-      <c r="D13" s="93">
+      <c r="D13" s="68">
         <v>2.355</v>
       </c>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A14" s="86">
+      <c r="A14" s="61">
         <v>12</v>
       </c>
-      <c r="B14" s="87">
+      <c r="B14" s="62">
         <v>2.681</v>
       </c>
-      <c r="C14" s="94">
+      <c r="C14" s="69">
         <v>2.2850000000000001</v>
       </c>
-      <c r="D14" s="95">
+      <c r="D14" s="70">
         <v>2.4119999999999999</v>
       </c>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="85"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A15" s="90">
+      <c r="A15" s="65">
         <v>13</v>
       </c>
-      <c r="B15" s="91">
+      <c r="B15" s="66">
         <v>2.65</v>
       </c>
-      <c r="C15" s="92">
+      <c r="C15" s="67">
         <v>2.331</v>
       </c>
-      <c r="D15" s="93">
+      <c r="D15" s="68">
         <v>2.4620000000000002</v>
       </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="85"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A16" s="86">
+      <c r="A16" s="61">
         <v>14</v>
       </c>
-      <c r="B16" s="87">
+      <c r="B16" s="62">
         <v>2.6240000000000001</v>
       </c>
-      <c r="C16" s="94">
+      <c r="C16" s="69">
         <v>2.371</v>
       </c>
-      <c r="D16" s="95">
+      <c r="D16" s="70">
         <v>2.5070000000000001</v>
       </c>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="85"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A17" s="90">
+      <c r="A17" s="65">
         <v>15</v>
       </c>
-      <c r="B17" s="91">
+      <c r="B17" s="66">
         <v>2.6019999999999999</v>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="67">
         <v>2.4089999999999998</v>
       </c>
-      <c r="D17" s="93">
+      <c r="D17" s="68">
         <v>2.5489999999999999</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="86">
+      <c r="A18" s="61">
         <v>16</v>
       </c>
-      <c r="B18" s="87">
+      <c r="B18" s="62">
         <v>2.5830000000000002</v>
       </c>
-      <c r="C18" s="94">
+      <c r="C18" s="69">
         <v>2.4430000000000001</v>
       </c>
-      <c r="D18" s="95">
+      <c r="D18" s="70">
         <v>2.585</v>
       </c>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="85"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A19" s="90">
+      <c r="A19" s="65">
         <v>17</v>
       </c>
-      <c r="B19" s="91">
+      <c r="B19" s="66">
         <v>2.5670000000000002</v>
       </c>
-      <c r="C19" s="92">
+      <c r="C19" s="67">
         <v>2.4750000000000001</v>
       </c>
-      <c r="D19" s="93">
+      <c r="D19" s="68">
         <v>2.62</v>
       </c>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="85"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A20" s="86">
+      <c r="A20" s="61">
         <v>18</v>
       </c>
-      <c r="B20" s="87">
+      <c r="B20" s="62">
         <v>2.552</v>
       </c>
-      <c r="C20" s="94">
+      <c r="C20" s="69">
         <v>2.504</v>
       </c>
-      <c r="D20" s="95">
+      <c r="D20" s="70">
         <v>2.6509999999999998</v>
       </c>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="85"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="90">
+      <c r="A21" s="65">
         <v>19</v>
       </c>
-      <c r="B21" s="91">
+      <c r="B21" s="66">
         <v>2.5390000000000001</v>
       </c>
-      <c r="C21" s="92">
+      <c r="C21" s="67">
         <v>2.532</v>
       </c>
-      <c r="D21" s="93">
+      <c r="D21" s="68">
         <v>2.681</v>
       </c>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="85"/>
-      <c r="J21" s="85"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A22" s="86">
+      <c r="A22" s="61">
         <v>20</v>
       </c>
-      <c r="B22" s="87">
+      <c r="B22" s="62">
         <v>2.528</v>
       </c>
-      <c r="C22" s="94">
+      <c r="C22" s="69">
         <v>2.5569999999999999</v>
       </c>
-      <c r="D22" s="95">
+      <c r="D22" s="70">
         <v>2.7090000000000001</v>
       </c>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="85"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A23" s="90">
+      <c r="A23" s="65">
         <v>21</v>
       </c>
-      <c r="B23" s="91">
+      <c r="B23" s="66">
         <v>2.5179999999999998</v>
       </c>
-      <c r="C23" s="92">
+      <c r="C23" s="67">
         <v>2.58</v>
       </c>
-      <c r="D23" s="93">
+      <c r="D23" s="68">
         <v>2.7330000000000001</v>
       </c>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="85"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A24" s="86">
+      <c r="A24" s="61">
         <v>22</v>
       </c>
-      <c r="B24" s="87">
+      <c r="B24" s="62">
         <v>2.508</v>
       </c>
-      <c r="C24" s="94">
+      <c r="C24" s="69">
         <v>2.6030000000000002</v>
       </c>
-      <c r="D24" s="95">
+      <c r="D24" s="70">
         <v>2.758</v>
       </c>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="85"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A25" s="90">
+      <c r="A25" s="65">
         <v>23</v>
       </c>
-      <c r="B25" s="91">
+      <c r="B25" s="66">
         <v>2.5</v>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="67">
         <v>2.6240000000000001</v>
       </c>
-      <c r="D25" s="93">
+      <c r="D25" s="68">
         <v>2.7810000000000001</v>
       </c>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="86">
+      <c r="A26" s="61">
         <v>24</v>
       </c>
-      <c r="B26" s="87">
+      <c r="B26" s="62">
         <v>2.492</v>
       </c>
-      <c r="C26" s="94">
+      <c r="C26" s="69">
         <v>2.6440000000000001</v>
       </c>
-      <c r="D26" s="95">
+      <c r="D26" s="70">
         <v>2.802</v>
       </c>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A27" s="90">
+      <c r="A27" s="65">
         <v>25</v>
       </c>
-      <c r="B27" s="91">
+      <c r="B27" s="66">
         <v>2.4849999999999999</v>
       </c>
-      <c r="C27" s="92">
+      <c r="C27" s="67">
         <v>2.6629999999999998</v>
       </c>
-      <c r="D27" s="93">
+      <c r="D27" s="68">
         <v>2.8220000000000001</v>
       </c>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A28" s="86">
+      <c r="A28" s="61">
         <v>26</v>
       </c>
-      <c r="B28" s="87">
+      <c r="B28" s="62">
         <v>2.4790000000000001</v>
       </c>
-      <c r="C28" s="94">
+      <c r="C28" s="69">
         <v>2.681</v>
       </c>
-      <c r="D28" s="95">
+      <c r="D28" s="70">
         <v>2.8410000000000002</v>
       </c>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A29" s="90">
+      <c r="A29" s="65">
         <v>27</v>
       </c>
-      <c r="B29" s="91">
+      <c r="B29" s="66">
         <v>2.4729999999999999</v>
       </c>
-      <c r="C29" s="92">
+      <c r="C29" s="67">
         <v>2.698</v>
       </c>
-      <c r="D29" s="93">
+      <c r="D29" s="68">
         <v>2.859</v>
       </c>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="86">
+      <c r="A30" s="61">
         <v>28</v>
       </c>
-      <c r="B30" s="87">
+      <c r="B30" s="62">
         <v>2.4670000000000001</v>
       </c>
-      <c r="C30" s="94">
+      <c r="C30" s="69">
         <v>2.714</v>
       </c>
-      <c r="D30" s="95">
+      <c r="D30" s="70">
         <v>2.8759999999999999</v>
       </c>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="90">
+      <c r="A31" s="65">
         <v>29</v>
       </c>
-      <c r="B31" s="91">
+      <c r="B31" s="66">
         <v>2.4620000000000002</v>
       </c>
-      <c r="C31" s="92">
+      <c r="C31" s="67">
         <v>2.73</v>
       </c>
-      <c r="D31" s="93">
+      <c r="D31" s="68">
         <v>2.8929999999999998</v>
       </c>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A32" s="86">
+      <c r="A32" s="61">
         <v>30</v>
       </c>
-      <c r="B32" s="87">
+      <c r="B32" s="62">
         <v>2.4569999999999999</v>
       </c>
-      <c r="C32" s="94">
+      <c r="C32" s="69">
         <v>2.7450000000000001</v>
       </c>
-      <c r="D32" s="95">
+      <c r="D32" s="70">
         <v>2.9079999999999999</v>
       </c>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A33" s="90">
+      <c r="A33" s="65">
         <v>40</v>
       </c>
-      <c r="B33" s="91">
+      <c r="B33" s="66">
         <v>2.423</v>
       </c>
-      <c r="C33" s="92">
+      <c r="C33" s="67">
         <v>2.8660000000000001</v>
       </c>
-      <c r="D33" s="93">
+      <c r="D33" s="68">
         <v>3.036</v>
       </c>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="60"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A34" s="86">
+      <c r="A34" s="61">
         <v>50</v>
       </c>
-      <c r="B34" s="87">
+      <c r="B34" s="62">
         <v>2.403</v>
       </c>
-      <c r="C34" s="94">
+      <c r="C34" s="69">
         <v>2.956</v>
       </c>
-      <c r="D34" s="95">
+      <c r="D34" s="70">
         <v>3.1280000000000001</v>
       </c>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A35" s="90">
+      <c r="A35" s="65">
         <v>60</v>
       </c>
-      <c r="B35" s="91">
+      <c r="B35" s="66">
         <v>2.39</v>
       </c>
-      <c r="C35" s="92">
+      <c r="C35" s="67">
         <v>3.0249999999999999</v>
       </c>
-      <c r="D35" s="93">
+      <c r="D35" s="68">
         <v>3.1989999999999998</v>
       </c>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="86">
+      <c r="A36" s="61">
         <v>80</v>
       </c>
-      <c r="B36" s="87">
+      <c r="B36" s="62">
         <v>2.3740000000000001</v>
       </c>
-      <c r="C36" s="94">
+      <c r="C36" s="69">
         <v>3.13</v>
       </c>
-      <c r="D36" s="95">
+      <c r="D36" s="70">
         <v>3.3105000000000002</v>
       </c>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="85"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="60"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A37" s="90">
+      <c r="A37" s="65">
         <v>100</v>
       </c>
-      <c r="B37" s="91">
+      <c r="B37" s="66">
         <v>2.3639999999999999</v>
       </c>
-      <c r="C37" s="92">
+      <c r="C37" s="67">
         <v>3.2069999999999999</v>
       </c>
-      <c r="D37" s="93">
+      <c r="D37" s="68">
         <v>3.383</v>
       </c>
-      <c r="E37" s="85"/>
-      <c r="F37" s="85"/>
-      <c r="G37" s="85"/>
-      <c r="H37" s="85"/>
-      <c r="I37" s="85"/>
-      <c r="J37" s="85"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="86">
+      <c r="A38" s="61">
         <v>150</v>
       </c>
-      <c r="B38" s="87">
+      <c r="B38" s="62">
         <v>2.3519999999999999</v>
       </c>
-      <c r="C38" s="94">
+      <c r="C38" s="69">
         <v>3.35</v>
       </c>
-      <c r="D38" s="95">
+      <c r="D38" s="70">
         <v>3.5150000000000001</v>
       </c>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="90">
+      <c r="A39" s="65">
         <v>200</v>
       </c>
-      <c r="B39" s="91">
+      <c r="B39" s="66">
         <v>2.3450000000000002</v>
       </c>
-      <c r="C39" s="92">
+      <c r="C39" s="67">
         <v>3.5</v>
       </c>
-      <c r="D39" s="93">
+      <c r="D39" s="68">
         <v>3.7</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A40" s="96">
+      <c r="A40" s="71">
         <v>1000</v>
       </c>
-      <c r="B40" s="97">
+      <c r="B40" s="72">
         <v>2.33</v>
       </c>
-      <c r="C40" s="98">
+      <c r="C40" s="73">
         <v>4</v>
       </c>
-      <c r="D40" s="99">
+      <c r="D40" s="74">
         <v>4.5</v>
       </c>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85"/>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
     </row>
     <row r="41" spans="1:10" ht="19.149999999999999" customHeight="1">
-      <c r="A41" s="100"/>
-      <c r="B41" s="100"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="101"/>
-      <c r="E41" s="102"/>
-      <c r="F41" s="102"/>
-      <c r="G41" s="102"/>
-      <c r="H41" s="102"/>
-      <c r="I41" s="102"/>
-      <c r="J41" s="102"/>
-    </row>
-    <row r="42" spans="1:10" ht="222.3" customHeight="1">
-      <c r="A42" s="103"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="106"/>
-      <c r="I42" s="106"/>
-      <c r="J42" s="102"/>
+      <c r="A41" s="75"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+    </row>
+    <row r="42" spans="1:10" ht="222.4" customHeight="1">
+      <c r="A42" s="78"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="77"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="347Jf9TL3m48LDSGCnG3/PjWCX8q8aRoMVPb/ZksoR3gKmMEEmQoAIe9rZxxRQ5Bmy7FKaPJ0KPGUDqwC7svaw==" saltValue="ieKBhAse6exqh0m7LiZqcQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -8158,147 +8147,147 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.875" style="107" customWidth="1"/>
-    <col min="2" max="2" width="23.6875" style="107" customWidth="1"/>
-    <col min="3" max="3" width="0.3125" style="107" customWidth="1"/>
-    <col min="4" max="16384" width="8.875" style="107" hidden="1"/>
+    <col min="1" max="1" width="15.875" style="82" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="82" customWidth="1"/>
+    <col min="3" max="3" width="0.375" style="82" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="82" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" customHeight="1">
-      <c r="A1" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="109" t="s">
-        <v>79</v>
+      <c r="A1" s="83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="84" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A2" s="110" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="111">
+      <c r="A2" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="86">
         <v>1000000</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A3" s="112" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="113">
+      <c r="A3" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="88">
         <v>1000000000</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A4" s="112" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="114">
+      <c r="A4" s="87" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="89">
         <v>1000000000000</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A5" s="112" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="114">
+      <c r="A5" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="89">
         <v>1000000</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A6" s="112" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="114">
+      <c r="A6" s="87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="89">
         <v>1000000000</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A7" s="112" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="114">
+      <c r="A7" s="87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="89">
         <v>1000000000000</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A8" s="115" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="114">
+      <c r="A8" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="89">
         <v>1000000</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A9" s="116" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="114">
+      <c r="A9" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="89">
         <v>1000000000</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A10" s="116" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="114">
+      <c r="A10" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="89">
         <v>1000000000000</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A11" s="116" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="114">
+      <c r="A11" s="91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="89">
         <v>1000000000000000</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A12" s="116" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="114">
+      <c r="A12" s="91" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="89">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A13" s="116" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="117">
+      <c r="A13" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="92">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A14" s="116" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="118">
+      <c r="A14" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="93">
         <v>568</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A15" s="119"/>
-      <c r="B15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
+      <c r="A16" s="96"/>
+      <c r="B16" s="97"/>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
-      <c r="A17" s="123"/>
-      <c r="B17" s="124"/>
+      <c r="A17" s="98"/>
+      <c r="B17" s="99"/>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="124"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="99"/>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="72"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="47"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="hCCuWl6xQvWO+nNlu7gVhg/GjJNYzKO6tAtqRPAiGHIJQMZC3okAYmb+67OIrMtwleGaB9XCiNe+i2wppzvSBA==" saltValue="k2a9kaXlk79rgIGuSyEadw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -8312,151 +8301,151 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="113.9375" style="125" customWidth="1"/>
-    <col min="2" max="3" width="8.8125" style="125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="0.125" style="125" customWidth="1"/>
-    <col min="5" max="5" width="2.9375" style="125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="7.0625" style="125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.75" style="125" hidden="1" customWidth="1"/>
-    <col min="8" max="16384" width="6.5" style="125" hidden="1"/>
+    <col min="1" max="1" width="114" style="100" customWidth="1"/>
+    <col min="2" max="3" width="8.875" style="100" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="0.125" style="100" customWidth="1"/>
+    <col min="5" max="5" width="3" style="100" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" style="100" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.75" style="100" hidden="1" customWidth="1"/>
+    <col min="8" max="16384" width="6.5" style="100" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="77.25" customHeight="1">
-      <c r="A1" s="126" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
+      <c r="A1" s="101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
     </row>
     <row r="2" spans="1:7" ht="29.65" customHeight="1">
-      <c r="A2" s="127" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
+      <c r="A2" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="3" spans="1:7" ht="49.15" customHeight="1">
-      <c r="A3" s="128" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
+      <c r="A3" s="103" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
     </row>
     <row r="4" spans="1:7" ht="39.6" customHeight="1">
-      <c r="A4" s="129" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
+      <c r="A4" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
     </row>
     <row r="5" spans="1:7" ht="387" customHeight="1">
-      <c r="A5" s="129" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
+      <c r="A5" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
     </row>
     <row r="6" spans="1:7" ht="74.849999999999994" customHeight="1">
-      <c r="A6" s="129" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
+      <c r="A6" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7" ht="22.9" customHeight="1">
-      <c r="A7" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
+      <c r="A7" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1">
-      <c r="A8" s="130" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
+      <c r="A8" s="105" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
     </row>
     <row r="9" spans="1:7" ht="38.25" customHeight="1">
-      <c r="A9" s="126" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
+      <c r="A9" s="101" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
     </row>
     <row r="10" spans="1:7" ht="46.9" customHeight="1">
-      <c r="A10" s="127" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
+      <c r="A10" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A11" s="131" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
+      <c r="A11" s="106" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
     </row>
     <row r="12" spans="1:7" ht="9" customHeight="1">
-      <c r="A12" s="132"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
+      <c r="A12" s="107"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z5tYmEgkKWhyUrhumpdcgr27d19uLpV/PwiVCvPEfaqiqHq4HGYZZi8RtXyEPLI7yIato67tqhGxLJs6EGiWUA==" saltValue="cJhZAuI46OYZPFyb3Sp+xw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.45" right="0.7" top="1.5" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait"/>
   <headerFooter>
